--- a/Employee_Reports_wi52/James Andrew Aquino Rodillo Q0546.xlsx
+++ b/Employee_Reports_wi52/James Andrew Aquino Rodillo Q0546.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
+        <bgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -87,6 +93,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -454,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -466,7 +475,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -569,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-118</v>
+        <v>-126</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -667,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1292,11 +1301,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-371</v>
+        <v>-379</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1341,11 +1350,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-161</v>
+        <v>-169</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1390,11 +1399,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-182</v>
+        <v>-190</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1439,11 +1448,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-156</v>
+        <v>-164</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1488,11 +1497,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-69</v>
+        <v>-77</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1537,11 +1546,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1586,11 +1595,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1635,11 +1644,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1684,11 +1693,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1733,11 +1742,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1782,11 +1791,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1831,11 +1840,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1868,11 +1877,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1888,7 +1897,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Docking Station (QNL Trainings)</t>
+          <t>Reshelving Cart (QNL Trainings)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
@@ -1896,20 +1905,20 @@
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>04-Aug-2026</t>
+          <t>18-Aug-2026</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>03-Aug-2028</t>
+          <t>17-Aug-2028</t>
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1925,7 +1934,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>RFID  Security  Gates.1 (QNL Trainings)</t>
+          <t>Library Bin (QNL Trainings)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr"/>
@@ -1933,20 +1942,20 @@
       <c r="E32" s="3" t="inlineStr"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>04-Aug-2026</t>
+          <t>18-Aug-2026</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>03-Aug-2028</t>
+          <t>17-Aug-2028</t>
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1962,7 +1971,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>IS0 55001 (Other Trainings)</t>
+          <t>Checkout Station (QNL Trainings)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
@@ -1970,20 +1979,20 @@
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>01-Oct-2024</t>
+          <t>18-Aug-2026</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>17-Aug-2028</t>
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>42</v>
+        <v>720</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -1999,7 +2008,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Material request Procedure (Other Trainings)</t>
+          <t>Docking Station2 (QNL Trainings)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
@@ -2007,28 +2016,139 @@
       <c r="E34" s="3" t="inlineStr"/>
       <c r="F34" s="3" t="inlineStr">
         <is>
+          <t>18-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>17-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>720</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Docking Station (QNL Trainings)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>04-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>03-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>706</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>01-Oct-2024</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>01-Oct-2026</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Material request Procedure (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
           <t>17-Nov-2024</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>17-Nov-2026</t>
         </is>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
